--- a/data/trans_camb/P16A12-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A12-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 6,19</t>
+          <t>-1,73; 6,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 5,99</t>
+          <t>-1,22; 6,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 9,84</t>
+          <t>1,87; 9,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 6,3</t>
+          <t>-1,33; 6,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 2,8</t>
+          <t>-3,84; 2,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 6,26</t>
+          <t>-0,55; 6,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 5,25</t>
+          <t>-0,47; 5,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 3,2</t>
+          <t>-1,61; 3,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,83</t>
+          <t>1,56; 6,71</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,0; 224,73</t>
+          <t>-30,38; 256,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,12; 203,37</t>
+          <t>-25,65; 204,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,72; 338,73</t>
+          <t>22,83; 375,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,01; 259,1</t>
+          <t>-35,3; 255,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-66,66; 129,69</t>
+          <t>-64,16; 139,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 291,61</t>
+          <t>-11,67; 264,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 172,13</t>
+          <t>-10,7; 170,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,21; 104,72</t>
+          <t>-30,03; 114,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,27; 226,1</t>
+          <t>24,35; 219,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 4,99</t>
+          <t>-1,5; 4,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 4,39</t>
+          <t>-1,97; 4,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 3,93</t>
+          <t>-2,05; 4,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 7,05</t>
+          <t>-0,49; 6,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 5,98</t>
+          <t>-1,29; 5,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 2,46</t>
+          <t>-3,22; 2,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,6</t>
+          <t>-0,16; 4,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 4,57</t>
+          <t>-0,41; 4,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,86</t>
+          <t>-1,92; 2,79</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,93; 132,51</t>
+          <t>-23,97; 119,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 106,88</t>
+          <t>-28,01; 112,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,12; 95,22</t>
+          <t>-32,81; 100,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 115,08</t>
+          <t>-5,41; 110,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 94,83</t>
+          <t>-13,68; 91,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,02; 40,82</t>
+          <t>-33,53; 46,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 82,62</t>
+          <t>-3,71; 81,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 82,04</t>
+          <t>-5,54; 80,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-20,27; 51,48</t>
+          <t>-24,66; 52,73</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 9,83</t>
+          <t>1,58; 9,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 2,58</t>
+          <t>-3,36; 2,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 10,12</t>
+          <t>2,7; 9,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 7,35</t>
+          <t>-1,57; 7,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 3,01</t>
+          <t>-5,07; 2,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 6,79</t>
+          <t>-1,07; 6,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 7,47</t>
+          <t>0,96; 7,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,84</t>
+          <t>-3,47; 1,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 7,3</t>
+          <t>1,91; 7,27</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,6; 303,17</t>
+          <t>17,14; 304,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-58,34; 78,35</t>
+          <t>-54,22; 80,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37,63; 321,95</t>
+          <t>35,4; 299,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,8; 129,95</t>
+          <t>-19,07; 143,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-50,02; 56,47</t>
+          <t>-53,92; 50,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 130,16</t>
+          <t>-11,75; 120,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,38; 143,98</t>
+          <t>11,53; 145,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,6; 36,32</t>
+          <t>-46,97; 34,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,25; 149,93</t>
+          <t>22,06; 152,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 4,1</t>
+          <t>-2,38; 4,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,49; 11,43</t>
+          <t>3,48; 11,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 7,21</t>
+          <t>0,18; 7,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 6,74</t>
+          <t>0,14; 6,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 5,32</t>
+          <t>-1,24; 5,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 3,49</t>
+          <t>-2,39; 3,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 4,61</t>
+          <t>-0,01; 4,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,06; 7,3</t>
+          <t>2,2; 7,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 4,1</t>
+          <t>-0,78; 4,02</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,12; 109,61</t>
+          <t>-36,39; 108,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>41,36; 313,21</t>
+          <t>54,43; 323,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 192,31</t>
+          <t>1,35; 198,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 192,3</t>
+          <t>-4,15; 202,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 157,8</t>
+          <t>-22,95; 169,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,51; 106,96</t>
+          <t>-37,99; 100,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 119,23</t>
+          <t>-0,45; 112,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>31,36; 188,49</t>
+          <t>37,18; 190,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 103,23</t>
+          <t>-11,29; 97,56</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 9,56</t>
+          <t>-0,92; 9,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 5,83</t>
+          <t>-2,93; 5,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,11; 10,02</t>
+          <t>1,25; 10,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 9,05</t>
+          <t>-2,61; 9,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 6,02</t>
+          <t>-4,46; 6,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 7,83</t>
+          <t>-2,06; 7,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 7,6</t>
+          <t>0,03; 7,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 4,45</t>
+          <t>-2,28; 4,88</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,22; 7,44</t>
+          <t>0,96; 7,63</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 326,11</t>
+          <t>-16,54; 319,25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-43,05; 225,77</t>
+          <t>-46,15; 198,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4,92; 333,13</t>
+          <t>9,39; 383,31</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-28,36; 147,18</t>
+          <t>-25,46; 148,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-43,23; 103,81</t>
+          <t>-40,24; 115,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-19,3; 127,31</t>
+          <t>-17,51; 135,52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 151,55</t>
+          <t>-2,11; 148,5</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-34,89; 80,85</t>
+          <t>-25,84; 102,59</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13,19; 145,54</t>
+          <t>9,23; 157,58</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 5,75</t>
+          <t>-3,15; 5,13</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 4,99</t>
+          <t>-2,96; 4,92</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4,6; 12,98</t>
+          <t>4,64; 13,35</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,93; 11,42</t>
+          <t>3,09; 11,68</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 7,49</t>
+          <t>-0,23; 7,47</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,41; 10,21</t>
+          <t>3,52; 10,86</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,12; 7,01</t>
+          <t>1,23; 6,93</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 5,18</t>
+          <t>-0,8; 4,86</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,13; 10,73</t>
+          <t>5,02; 10,49</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-37,88; 149,36</t>
+          <t>-44,63; 141,77</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-38,85; 144,46</t>
+          <t>-41,54; 143,03</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>55,35; 349,14</t>
+          <t>50,21; 381,74</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>40,55; 542,8</t>
+          <t>43,27; 635,62</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 358,08</t>
+          <t>-16,22; 363,99</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>51,93; 490,91</t>
+          <t>53,23; 638,59</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,53; 218,75</t>
+          <t>19,32; 215,46</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 153,01</t>
+          <t>-16,32; 143,43</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>75,26; 339,63</t>
+          <t>81,53; 319,07</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 4,26</t>
+          <t>-1,5; 4,52</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,02; 7,4</t>
+          <t>0,78; 7,21</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 4,14</t>
+          <t>-1,43; 4,42</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 4,67</t>
+          <t>-1,03; 4,68</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 4,25</t>
+          <t>-1,5; 4,68</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 0,36</t>
+          <t>-6,14; 0,12</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 3,57</t>
+          <t>-0,44; 3,53</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,19</t>
+          <t>0,72; 5,04</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 1,21</t>
+          <t>-3,17; 1,43</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 74,86</t>
+          <t>-18,73; 84,51</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>12,25; 134,81</t>
+          <t>9,86; 131,72</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 72,96</t>
+          <t>-18,01; 80,94</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 91,14</t>
+          <t>-14,68; 91,8</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 87,2</t>
+          <t>-21,16; 85,67</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-67,42; 3,11</t>
+          <t>-72,52; 1,4</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 65,48</t>
+          <t>-6,19; 62,35</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>9,15; 91,06</t>
+          <t>9,12; 90,23</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-43,94; 20,15</t>
+          <t>-42,34; 23,82</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 2,8</t>
+          <t>-2,2; 2,96</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,76</t>
+          <t>0,19; 5,44</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 1,97</t>
+          <t>-4,75; 1,76</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,15</t>
+          <t>-2,36; 2,34</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,89</t>
+          <t>0,65; 6,23</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,47</t>
+          <t>-1,76; 2,55</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 1,97</t>
+          <t>-1,54; 2,06</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,98</t>
+          <t>1,37; 4,95</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 1,45</t>
+          <t>-2,84; 1,35</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-28,93; 61,56</t>
+          <t>-31,57; 61,88</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>7,77; 130,13</t>
+          <t>1,84; 114,13</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-62,67; 35,32</t>
+          <t>-62,43; 32,6</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-38,11; 48,23</t>
+          <t>-35,45; 52,47</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6,17; 131,08</t>
+          <t>8,38; 142,99</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-24,85; 58,97</t>
+          <t>-25,91; 60,52</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-23,41; 40,57</t>
+          <t>-23,14; 41,2</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>17,63; 101,72</t>
+          <t>20,44; 99,67</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-41,85; 26,75</t>
+          <t>-46,79; 25,24</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,9</t>
+          <t>0,52; 2,91</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,99</t>
+          <t>1,56; 4,02</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,9</t>
+          <t>0,61; 3,76</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,71</t>
+          <t>1,17; 3,68</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,96</t>
+          <t>0,56; 3,08</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,9</t>
+          <t>-0,46; 1,98</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,96</t>
+          <t>1,19; 2,92</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,17</t>
+          <t>1,31; 3,14</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,69</t>
+          <t>0,56; 2,57</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>9,13; 56,54</t>
+          <t>9,37; 59,52</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>24,88; 78,04</t>
+          <t>23,78; 77,83</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>14,5; 75,76</t>
+          <t>10,52; 74,64</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>17,73; 65,63</t>
+          <t>17,62; 68,76</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>6,44; 53,84</t>
+          <t>8,55; 55,36</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 33,87</t>
+          <t>-6,91; 35,7</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>18,82; 53,44</t>
+          <t>19,2; 53,92</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>22,72; 58,32</t>
+          <t>21,18; 57,99</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>9,74; 48,69</t>
+          <t>9,32; 47,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A12-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A12-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,49</t>
+          <t>5,42</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,32</t>
+          <t>3,48</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,44</t>
+          <t>4,45</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 6,08</t>
+          <t>-1,92; 5,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 6,18</t>
+          <t>-1,48; 6,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 9,69</t>
+          <t>1,81; 9,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 6,27</t>
+          <t>-0,86; 6,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 2,84</t>
+          <t>-4,17; 2,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 6,2</t>
+          <t>-0,36; 6,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 5,1</t>
+          <t>-0,33; 5,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,36</t>
+          <t>-1,85; 3,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,71</t>
+          <t>1,87; 6,96</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>125,31%</t>
+          <t>123,8%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>105,6%</t>
+          <t>105,71%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,38; 256,32</t>
+          <t>-33,78; 187,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,65; 204,02</t>
+          <t>-29,81; 220,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,83; 375,35</t>
+          <t>20,38; 316,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,3; 255,9</t>
+          <t>-23,37; 315,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,16; 139,45</t>
+          <t>-69,0; 109,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 264,07</t>
+          <t>-7,44; 255,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 170,39</t>
+          <t>-8,2; 170,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,03; 114,42</t>
+          <t>-32,63; 108,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,35; 219,45</t>
+          <t>30,7; 239,0</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,36</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 4,84</t>
+          <t>-1,8; 4,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 4,3</t>
+          <t>-1,56; 4,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 4,1</t>
+          <t>-2,19; 4,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 6,88</t>
+          <t>-0,66; 6,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 5,88</t>
+          <t>-1,02; 6,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 2,86</t>
+          <t>-3,89; 2,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,64</t>
+          <t>-0,22; 4,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 4,45</t>
+          <t>-0,43; 4,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,79</t>
+          <t>-1,83; 2,39</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-3,18%</t>
+          <t>-4,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,97; 119,01</t>
+          <t>-26,14; 117,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,01; 112,24</t>
+          <t>-23,38; 110,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-32,81; 100,07</t>
+          <t>-32,9; 99,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 110,51</t>
+          <t>-7,56; 109,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 91,96</t>
+          <t>-11,37; 106,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,53; 46,18</t>
+          <t>-37,57; 37,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 81,13</t>
+          <t>-3,35; 85,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 80,88</t>
+          <t>-6,64; 76,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 52,73</t>
+          <t>-22,1; 42,84</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,55</t>
+          <t>6,43</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,91</t>
+          <t>2,79</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,67</t>
+          <t>4,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 9,82</t>
+          <t>1,57; 9,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,6</t>
+          <t>-3,71; 2,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 9,73</t>
+          <t>2,92; 10,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 7,51</t>
+          <t>-1,25; 7,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 2,78</t>
+          <t>-4,97; 3,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 6,72</t>
+          <t>-0,91; 6,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 7,0</t>
+          <t>1,27; 7,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,75</t>
+          <t>-3,36; 1,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,27</t>
+          <t>1,61; 6,98</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>137,28%</t>
+          <t>134,75%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>74,3%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,14; 304,15</t>
+          <t>21,82; 314,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-54,22; 80,17</t>
+          <t>-55,46; 85,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,4; 299,78</t>
+          <t>40,23; 309,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 143,45</t>
+          <t>-15,19; 144,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-53,92; 50,24</t>
+          <t>-53,54; 55,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 120,55</t>
+          <t>-9,49; 127,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,53; 145,32</t>
+          <t>17,14; 151,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-46,97; 34,65</t>
+          <t>-44,59; 38,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,06; 152,03</t>
+          <t>20,35; 148,1</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,45</t>
+          <t>3,41</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>1,74</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,75</t>
+          <t>2,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 4,02</t>
+          <t>-2,19; 4,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,48; 11,47</t>
+          <t>3,43; 11,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 7,24</t>
+          <t>0,19; 7,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 6,9</t>
+          <t>0,19; 7,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 5,47</t>
+          <t>-1,25; 5,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 3,43</t>
+          <t>-1,04; 4,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,53</t>
+          <t>-0,25; 4,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 7,44</t>
+          <t>2,11; 7,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 4,02</t>
+          <t>0,26; 4,63</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>51,32%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,39; 108,6</t>
+          <t>-33,33; 128,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>54,43; 323,94</t>
+          <t>48,89; 319,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,35; 198,63</t>
+          <t>0,05; 204,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 202,71</t>
+          <t>-1,39; 200,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 169,49</t>
+          <t>-21,79; 168,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,99; 100,96</t>
+          <t>-17,04; 123,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 112,54</t>
+          <t>-6,12; 118,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>37,18; 190,82</t>
+          <t>32,18; 177,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 97,56</t>
+          <t>4,22; 120,4</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5,44</t>
+          <t>4,59</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,35</t>
+          <t>2,82</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,45</t>
+          <t>3,74</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 9,07</t>
+          <t>-0,57; 8,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 5,41</t>
+          <t>-2,36; 5,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,25; 10,02</t>
+          <t>0,09; 8,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 9,24</t>
+          <t>-2,58; 9,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 6,51</t>
+          <t>-5,04; 6,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 7,86</t>
+          <t>-2,1; 7,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,03; 7,74</t>
+          <t>-0,01; 7,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 4,88</t>
+          <t>-2,57; 4,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,96; 7,63</t>
+          <t>0,27; 6,72</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>114,3%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>54,95%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 319,25</t>
+          <t>-11,34; 313,07</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-46,15; 198,48</t>
+          <t>-36,5; 197,22</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9,39; 383,31</t>
+          <t>-1,12; 300,09</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,46; 148,53</t>
+          <t>-22,92; 148,48</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-40,24; 115,49</t>
+          <t>-44,24; 105,45</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 135,52</t>
+          <t>-19,04; 128,73</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 148,5</t>
+          <t>-2,66; 148,34</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-25,84; 102,59</t>
+          <t>-30,1; 93,48</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>9,23; 157,58</t>
+          <t>2,4; 132,33</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8,68</t>
+          <t>8,69</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,08</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7,95</t>
+          <t>7,93</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 5,13</t>
+          <t>-2,85; 5,03</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 4,92</t>
+          <t>-3,05; 4,63</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4,64; 13,35</t>
+          <t>4,49; 13,03</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,09; 11,68</t>
+          <t>2,82; 11,69</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 7,47</t>
+          <t>-0,4; 7,59</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,52; 10,86</t>
+          <t>3,54; 10,48</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,93</t>
+          <t>1,24; 7,38</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 4,86</t>
+          <t>-0,45; 4,86</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,02; 10,49</t>
+          <t>5,27; 10,68</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>153,74%</t>
+          <t>153,91%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>207,15%</t>
+          <t>206,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>175,82%</t>
+          <t>175,28%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-44,63; 141,77</t>
+          <t>-39,67; 143,77</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-41,54; 143,03</t>
+          <t>-41,28; 125,7</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>50,21; 381,74</t>
+          <t>49,73; 372,21</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>43,27; 635,62</t>
+          <t>49,06; 642,4</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 363,99</t>
+          <t>-24,64; 382,07</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>53,23; 638,59</t>
+          <t>58,71; 595,95</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,32; 215,46</t>
+          <t>17,63; 220,35</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 143,43</t>
+          <t>-9,11; 151,7</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>81,53; 319,07</t>
+          <t>86,08; 317,32</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-2,2</t>
+          <t>-0,7</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,7</t>
+          <t>0,56</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 4,52</t>
+          <t>-1,5; 4,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,21</t>
+          <t>0,98; 7,22</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 4,42</t>
+          <t>-0,81; 4,7</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 4,68</t>
+          <t>-1,09; 4,58</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 4,68</t>
+          <t>-1,41; 4,38</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 0,12</t>
+          <t>-3,25; 1,48</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,53</t>
+          <t>-0,37; 3,69</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,04</t>
+          <t>0,6; 5,0</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 1,43</t>
+          <t>-1,46; 2,3</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-34,15%</t>
+          <t>-10,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-10,66%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 84,51</t>
+          <t>-18,36; 83,44</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>9,86; 131,72</t>
+          <t>12,76; 134,97</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 80,94</t>
+          <t>-10,79; 93,51</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 91,8</t>
+          <t>-14,96; 86,55</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-21,16; 85,67</t>
+          <t>-17,71; 88,23</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-72,52; 1,4</t>
+          <t>-39,93; 29,88</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 62,35</t>
+          <t>-6,47; 63,04</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>9,12; 90,23</t>
+          <t>7,83; 91,95</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-42,34; 23,82</t>
+          <t>-19,21; 40,11</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>0,57</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,96</t>
+          <t>-1,97; 2,76</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,19; 5,44</t>
+          <t>0,49; 5,29</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 1,76</t>
+          <t>-1,78; 2,81</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,34</t>
+          <t>-2,45; 2,28</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,23</t>
+          <t>0,72; 6,01</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,55</t>
+          <t>-1,71; 2,61</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 2,06</t>
+          <t>-1,53; 1,85</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,95</t>
+          <t>1,24; 4,94</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 1,35</t>
+          <t>-1,06; 2,28</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-15,47%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-5,19%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-31,57; 61,88</t>
+          <t>-27,97; 60,97</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1,84; 114,13</t>
+          <t>6,8; 110,5</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-62,43; 32,6</t>
+          <t>-23,98; 58,05</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-35,45; 52,47</t>
+          <t>-37,41; 54,75</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>8,38; 142,99</t>
+          <t>9,03; 135,78</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-25,91; 60,52</t>
+          <t>-24,31; 63,51</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 41,2</t>
+          <t>-23,98; 38,23</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>20,44; 99,67</t>
+          <t>18,41; 97,7</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-46,79; 25,24</t>
+          <t>-16,74; 45,9</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2,57</t>
+          <t>3,08</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1,69</t>
+          <t>2,2</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,91</t>
+          <t>0,44; 2,9</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,02</t>
+          <t>1,48; 3,88</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,76</t>
+          <t>1,86; 4,2</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,68</t>
+          <t>1,2; 3,66</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,08</t>
+          <t>0,53; 3,17</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,98</t>
+          <t>0,25; 2,32</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,92</t>
+          <t>1,21; 2,92</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,14</t>
+          <t>1,42; 3,16</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,57</t>
+          <t>1,43; 2,99</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>9,37; 59,52</t>
+          <t>6,85; 56,89</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>23,78; 77,83</t>
+          <t>23,48; 77,15</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>10,52; 74,64</t>
+          <t>30,14; 82,86</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>17,62; 68,76</t>
+          <t>17,89; 66,88</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>8,55; 55,36</t>
+          <t>7,87; 56,4</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 35,7</t>
+          <t>3,46; 41,26</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>19,2; 53,92</t>
+          <t>19,11; 53,55</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>21,18; 57,99</t>
+          <t>22,47; 57,97</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>9,32; 47,17</t>
+          <t>22,88; 56,3</t>
         </is>
       </c>
     </row>
